--- a/pdks_ekim_gunluk_calisma_saatleri.xlsx
+++ b/pdks_ekim_gunluk_calisma_saatleri.xlsx
@@ -4689,10 +4689,10 @@
       <c r="R51" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S51" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="T51" s="7" t="n"/>
+      <c r="S51" s="7" t="n"/>
+      <c r="T51" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="U51" s="6" t="n">
         <v>18.5</v>
       </c>
@@ -5366,38 +5366,38 @@
           <t>KALİTE</t>
         </is>
       </c>
-      <c r="D60" s="9" t="n">
-        <v>7.5</v>
+      <c r="D60" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="E60" s="9" t="n">
         <v>7.5</v>
       </c>
       <c r="F60" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G60" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G60" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H60" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I60" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J60" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K60" s="6" t="n">
-        <v>8</v>
+      <c r="H60" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I60" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>7.5</v>
       </c>
       <c r="L60" s="6" t="n">
         <v>8</v>
       </c>
       <c r="M60" s="6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N60" s="9" t="n">
-        <v>7.5</v>
+        <v>8</v>
+      </c>
+      <c r="N60" s="6" t="n">
+        <v>8.5</v>
       </c>
       <c r="O60" s="9" t="n">
         <v>7.5</v>
@@ -5405,19 +5405,21 @@
       <c r="P60" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v>8</v>
+      <c r="Q60" s="9" t="n">
+        <v>7.5</v>
       </c>
       <c r="R60" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="S60" s="14" t="n"/>
+      <c r="S60" s="6" t="n">
+        <v>8</v>
+      </c>
       <c r="T60" s="14" t="n"/>
       <c r="U60" s="8" t="n"/>
-      <c r="V60" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W60" s="14" t="n"/>
+      <c r="V60" s="14" t="n"/>
+      <c r="W60" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="X60" s="14" t="n"/>
       <c r="Y60" s="14" t="n"/>
       <c r="Z60" s="14" t="n"/>
@@ -5430,10 +5432,10 @@
       <c r="AG60" s="14" t="n"/>
       <c r="AH60" s="14" t="n"/>
       <c r="AI60" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ60" s="11" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
@@ -8081,10 +8083,10 @@
       <c r="F94" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="G94" s="8" t="n"/>
-      <c r="H94" s="9" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="G94" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H94" s="14" t="n"/>
       <c r="I94" s="9" t="n">
         <v>7.5</v>
       </c>
@@ -8130,7 +8132,9 @@
       <c r="W94" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="X94" s="14" t="n"/>
+      <c r="X94" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="Y94" s="14" t="n"/>
       <c r="Z94" s="14" t="n"/>
       <c r="AA94" s="14" t="n"/>
@@ -8142,10 +8146,10 @@
       <c r="AG94" s="14" t="n"/>
       <c r="AH94" s="14" t="n"/>
       <c r="AI94" s="10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ94" s="11" t="n">
-        <v>142.5</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" ht="19" customHeight="1">
@@ -10405,10 +10409,10 @@
       <c r="R123" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S123" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="T123" s="7" t="n"/>
+      <c r="S123" s="7" t="n"/>
+      <c r="T123" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="U123" s="6" t="n">
         <v>10.5</v>
       </c>
@@ -12723,10 +12727,10 @@
       <c r="R152" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S152" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="T152" s="14" t="n"/>
+      <c r="S152" s="14" t="n"/>
+      <c r="T152" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="U152" s="6" t="n">
         <v>10.5</v>
       </c>
@@ -16480,12 +16484,10 @@
       <c r="O202" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="P202" s="6" t="n">
+      <c r="P202" s="14" t="n"/>
+      <c r="Q202" s="6" t="n">
         <v>9.5</v>
       </c>
-      <c r="Q202" s="9" t="n">
-        <v>7.5</v>
-      </c>
       <c r="R202" s="9" t="n">
         <v>7.5</v>
       </c>
@@ -16504,7 +16506,9 @@
       <c r="W202" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="X202" s="14" t="n"/>
+      <c r="X202" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="Y202" s="14" t="n"/>
       <c r="Z202" s="14" t="n"/>
       <c r="AA202" s="14" t="n"/>
@@ -18396,29 +18400,27 @@
         <v>8</v>
       </c>
       <c r="G227" s="8" t="n"/>
-      <c r="H227" s="6" t="n">
+      <c r="H227" s="7" t="n"/>
+      <c r="I227" s="6" t="n">
         <v>9.5</v>
       </c>
-      <c r="I227" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J227" s="6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="K227" s="9" t="n">
-        <v>7.5</v>
+      <c r="J227" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K227" s="6" t="n">
+        <v>8.5</v>
       </c>
       <c r="L227" s="9" t="n">
         <v>7.5</v>
       </c>
       <c r="M227" s="9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N227" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="O227" s="9" t="n">
-        <v>7.5</v>
+      <c r="O227" s="6" t="n">
+        <v>14.09</v>
       </c>
       <c r="P227" s="6" t="n">
         <v>8</v>
@@ -18436,10 +18438,12 @@
         <v>4.5</v>
       </c>
       <c r="U227" s="8" t="n"/>
-      <c r="V227" s="6" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="W227" s="7" t="n"/>
+      <c r="V227" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="W227" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="X227" s="9" t="n">
         <v>7</v>
       </c>
@@ -18457,7 +18461,7 @@
         <v>18</v>
       </c>
       <c r="AJ227" s="11" t="n">
-        <v>137.77</v>
+        <v>137.41</v>
       </c>
     </row>
     <row r="228" ht="19" customHeight="1">
@@ -18577,11 +18581,11 @@
       <c r="H229" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="I229" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="J229" s="9" t="n">
-        <v>7.5</v>
+      <c r="I229" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J229" s="6" t="n">
+        <v>15</v>
       </c>
       <c r="K229" s="7" t="n"/>
       <c r="L229" s="6" t="n">
@@ -18629,7 +18633,7 @@
         <v>14</v>
       </c>
       <c r="AJ229" s="11" t="n">
-        <v>114.5</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="230" ht="19" customHeight="1">
@@ -19310,22 +19314,22 @@
       <c r="G238" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="H238" s="6" t="n">
+      <c r="H238" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I238" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="I238" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="J238" s="14" t="n"/>
-      <c r="K238" s="6" t="n">
-        <v>14.5</v>
+      <c r="J238" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K238" s="9" t="n">
+        <v>7</v>
       </c>
       <c r="L238" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="M238" s="9" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="M238" s="14" t="n"/>
       <c r="N238" s="9" t="n">
         <v>7.5</v>
       </c>
@@ -19373,7 +19377,7 @@
         <v>20</v>
       </c>
       <c r="AJ238" s="11" t="n">
-        <v>158.5</v>
+        <v>151</v>
       </c>
     </row>
     <row r="239" ht="19" customHeight="1">
@@ -19703,13 +19707,13 @@
       <c r="D243" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="E243" s="6" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F243" s="7" t="n"/>
-      <c r="G243" s="9" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="E243" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F243" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G243" s="8" t="n"/>
       <c r="H243" s="9" t="n">
         <v>7.5</v>
       </c>
@@ -19725,10 +19729,10 @@
       <c r="L243" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="M243" s="7" t="n"/>
-      <c r="N243" s="9" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="M243" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N243" s="8" t="n"/>
       <c r="O243" s="9" t="n">
         <v>7.5</v>
       </c>
@@ -19744,17 +19748,19 @@
       <c r="S243" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="T243" s="7" t="n"/>
-      <c r="U243" s="9" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="T243" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U243" s="8" t="n"/>
       <c r="V243" s="9" t="n">
         <v>7.5</v>
       </c>
       <c r="W243" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="X243" s="7" t="n"/>
+      <c r="X243" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="Y243" s="7" t="n"/>
       <c r="Z243" s="7" t="n"/>
       <c r="AA243" s="7" t="n"/>
@@ -19766,10 +19772,10 @@
       <c r="AG243" s="7" t="n"/>
       <c r="AH243" s="7" t="n"/>
       <c r="AI243" s="10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ243" s="11" t="n">
-        <v>134.7</v>
+        <v>135</v>
       </c>
     </row>
     <row r="244" ht="19" customHeight="1">
@@ -22281,15 +22287,17 @@
       <c r="D277" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="E277" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F277" s="7" t="n"/>
-      <c r="G277" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H277" s="9" t="n">
-        <v>7.5</v>
+      <c r="E277" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F277" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G277" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H277" s="6" t="n">
+        <v>15.23</v>
       </c>
       <c r="I277" s="6" t="n">
         <v>8.5</v>
@@ -22309,11 +22317,9 @@
       <c r="N277" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="O277" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="P277" s="9" t="n">
-        <v>7.5</v>
+      <c r="O277" s="7" t="n"/>
+      <c r="P277" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="Q277" s="9" t="n">
         <v>7.5</v>
@@ -22321,7 +22327,9 @@
       <c r="R277" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S277" s="7" t="n"/>
+      <c r="S277" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="T277" s="6" t="n">
         <v>10.5</v>
       </c>
@@ -22346,10 +22354,10 @@
       <c r="AG277" s="7" t="n"/>
       <c r="AH277" s="7" t="n"/>
       <c r="AI277" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ277" s="11" t="n">
-        <v>143</v>
+        <v>152.73</v>
       </c>
     </row>
     <row r="278" ht="19" customHeight="1">
@@ -23034,38 +23042,38 @@
           <t>KALİTE</t>
         </is>
       </c>
-      <c r="D287" s="9" t="n">
-        <v>7.5</v>
+      <c r="D287" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="E287" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="F287" s="6" t="n">
+      <c r="F287" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G287" s="6" t="n">
         <v>9.5</v>
       </c>
-      <c r="G287" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H287" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I287" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J287" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="K287" s="6" t="n">
-        <v>8</v>
+      <c r="H287" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I287" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J287" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K287" s="9" t="n">
+        <v>7.5</v>
       </c>
       <c r="L287" s="6" t="n">
         <v>8</v>
       </c>
       <c r="M287" s="6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="N287" s="9" t="n">
-        <v>7.5</v>
+        <v>8</v>
+      </c>
+      <c r="N287" s="6" t="n">
+        <v>8.5</v>
       </c>
       <c r="O287" s="9" t="n">
         <v>7.5</v>
@@ -23073,19 +23081,21 @@
       <c r="P287" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="Q287" s="6" t="n">
-        <v>8</v>
+      <c r="Q287" s="9" t="n">
+        <v>7.5</v>
       </c>
       <c r="R287" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="S287" s="7" t="n"/>
+      <c r="S287" s="6" t="n">
+        <v>8</v>
+      </c>
       <c r="T287" s="7" t="n"/>
       <c r="U287" s="8" t="n"/>
-      <c r="V287" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W287" s="7" t="n"/>
+      <c r="V287" s="7" t="n"/>
+      <c r="W287" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="X287" s="7" t="n"/>
       <c r="Y287" s="7" t="n"/>
       <c r="Z287" s="7" t="n"/>
@@ -23098,10 +23108,10 @@
       <c r="AG287" s="7" t="n"/>
       <c r="AH287" s="7" t="n"/>
       <c r="AI287" s="10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ287" s="11" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="288" ht="19" customHeight="1">
@@ -23500,13 +23510,13 @@
           <t>KAPI GÖREVLİSİ</t>
         </is>
       </c>
-      <c r="D293" s="7" t="n"/>
+      <c r="D293" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="E293" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="F293" s="9" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="F293" s="7" t="n"/>
       <c r="G293" s="9" t="n">
         <v>7.5</v>
       </c>
@@ -23522,10 +23532,12 @@
       <c r="K293" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="L293" s="6" t="n">
-        <v>14.37</v>
-      </c>
-      <c r="M293" s="7" t="n"/>
+      <c r="L293" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="M293" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="N293" s="9" t="n">
         <v>7.5</v>
       </c>
@@ -23550,10 +23562,10 @@
       <c r="U293" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="V293" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W293" s="7" t="n"/>
+      <c r="V293" s="7" t="n"/>
+      <c r="W293" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="X293" s="7" t="n"/>
       <c r="Y293" s="7" t="n"/>
       <c r="Z293" s="7" t="n"/>
@@ -23566,10 +23578,10 @@
       <c r="AG293" s="7" t="n"/>
       <c r="AH293" s="7" t="n"/>
       <c r="AI293" s="10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ293" s="11" t="n">
-        <v>133.87</v>
+        <v>134</v>
       </c>
     </row>
     <row r="294" ht="19" customHeight="1">
@@ -23767,10 +23779,12 @@
       <c r="H296" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="I296" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="J296" s="14" t="n"/>
+      <c r="I296" s="9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J296" s="9" t="n">
+        <v>7.5</v>
+      </c>
       <c r="K296" s="9" t="n">
         <v>7.5</v>
       </c>
@@ -23814,10 +23828,10 @@
       <c r="AG296" s="14" t="n"/>
       <c r="AH296" s="14" t="n"/>
       <c r="AI296" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ296" s="11" t="n">
-        <v>114.5</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="297" ht="19" customHeight="1">
@@ -23834,11 +23848,9 @@
           <t>DİĞER</t>
         </is>
       </c>
-      <c r="D297" s="9" t="n">
-        <v>7.5</v>
-      </c>
+      <c r="D297" s="7" t="n"/>
       <c r="E297" s="6" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="F297" s="6" t="n">
         <v>10.5</v>
@@ -23886,7 +23898,7 @@
       <c r="AG297" s="7" t="n"/>
       <c r="AH297" s="7" t="n"/>
       <c r="AI297" s="10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ297" s="11" t="n">
         <v>103</v>

--- a/pdks_ekim_gunluk_calisma_saatleri.xlsx
+++ b/pdks_ekim_gunluk_calisma_saatleri.xlsx
@@ -3373,7 +3373,7 @@
         <v>8</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="G35" s="8" t="n"/>
       <c r="H35" s="9" t="n">
@@ -3433,7 +3433,7 @@
         <v>15</v>
       </c>
       <c r="AJ35" s="11" t="n">
-        <v>116.5</v>
+        <v>115.62</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
@@ -6010,7 +6010,7 @@
         <v>7.5</v>
       </c>
       <c r="W67" s="6" t="n">
-        <v>10</v>
+        <v>10.37</v>
       </c>
       <c r="X67" s="7" t="n"/>
       <c r="Y67" s="7" t="n"/>
@@ -6027,7 +6027,7 @@
         <v>17</v>
       </c>
       <c r="AJ67" s="11" t="n">
-        <v>167.5</v>
+        <v>167.87</v>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
@@ -7601,7 +7601,7 @@
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.5</v>
+        <v>1.02</v>
       </c>
       <c r="E88" s="9" t="n">
         <v>7.5</v>
@@ -7663,7 +7663,7 @@
         <v>14</v>
       </c>
       <c r="AJ88" s="11" t="n">
-        <v>96.92</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="89" ht="19" customHeight="1">
@@ -7707,9 +7707,7 @@
       <c r="N89" s="8" t="n"/>
       <c r="O89" s="7" t="n"/>
       <c r="P89" s="7" t="n"/>
-      <c r="Q89" s="9" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="Q89" s="7" t="n"/>
       <c r="R89" s="9" t="n">
         <v>7.5</v>
       </c>
@@ -7736,10 +7734,10 @@
       <c r="AG89" s="7" t="n"/>
       <c r="AH89" s="7" t="n"/>
       <c r="AI89" s="10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ89" s="11" t="n">
-        <v>89</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="90" ht="19" customHeight="1">
@@ -9265,7 +9263,7 @@
       </c>
       <c r="C109" s="5" t="inlineStr"/>
       <c r="D109" s="9" t="n">
-        <v>1</v>
+        <v>7.5</v>
       </c>
       <c r="E109" s="9" t="n">
         <v>6.5</v>
@@ -9309,7 +9307,7 @@
         <v>5</v>
       </c>
       <c r="AJ109" s="11" t="n">
-        <v>27</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="110" ht="19" customHeight="1">
@@ -12317,7 +12315,7 @@
       <c r="J147" s="7" t="n"/>
       <c r="K147" s="7" t="n"/>
       <c r="L147" s="9" t="n">
-        <v>4.5</v>
+        <v>3.43</v>
       </c>
       <c r="M147" s="6" t="n">
         <v>10.5</v>
@@ -12361,7 +12359,7 @@
         <v>9</v>
       </c>
       <c r="AJ147" s="11" t="n">
-        <v>82.5</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="148" ht="19" customHeight="1">
@@ -18003,7 +18001,7 @@
         <v>7.5</v>
       </c>
       <c r="H222" s="9" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="I222" s="9" t="n">
         <v>7.5</v>
@@ -18028,7 +18026,7 @@
         <v>7.5</v>
       </c>
       <c r="Q222" s="9" t="n">
-        <v>7.5</v>
+        <v>5.42</v>
       </c>
       <c r="R222" s="9" t="n">
         <v>7.5</v>
@@ -18065,7 +18063,7 @@
         <v>20</v>
       </c>
       <c r="AJ222" s="11" t="n">
-        <v>142</v>
+        <v>139.2</v>
       </c>
     </row>
     <row r="223" ht="19" customHeight="1">
@@ -20574,7 +20572,7 @@
         <v>11.5</v>
       </c>
       <c r="E254" s="6" t="n">
-        <v>8</v>
+        <v>7.880000000000001</v>
       </c>
       <c r="F254" s="6" t="n">
         <v>8.5</v>
@@ -20617,7 +20615,7 @@
         <v>6</v>
       </c>
       <c r="AJ254" s="11" t="n">
-        <v>50.5</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="255" ht="19" customHeight="1">
